--- a/etf_holdings/2026-08-25_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:32</t>
+          <t>2026-08-25 10:24:17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:33</t>
+          <t>2026-08-25 10:24:18</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:33</t>
+          <t>2026-08-25 10:24:18</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:33</t>
+          <t>2026-08-25 10:24:18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:33</t>
+          <t>2026-08-25 10:24:18</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:33</t>
+          <t>2026-08-25 10:24:18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:33</t>
+          <t>2026-08-25 10:24:18</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:33</t>
+          <t>2026-08-25 10:24:18</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:33</t>
+          <t>2026-08-25 10:24:18</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:33</t>
+          <t>2026-08-25 10:24:18</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:33</t>
+          <t>2026-08-25 10:24:18</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:33</t>
+          <t>2026-08-25 10:24:18</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:33</t>
+          <t>2026-08-25 10:24:18</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:33</t>
+          <t>2026-08-25 10:24:18</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:33</t>
+          <t>2026-08-25 10:24:18</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:35</t>
+          <t>2026-08-25 10:24:19</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:36</t>
+          <t>2026-08-25 10:24:21</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:36</t>
+          <t>2026-08-25 10:24:21</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:36</t>
+          <t>2026-08-25 10:24:21</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:36</t>
+          <t>2026-08-25 10:24:21</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:36</t>
+          <t>2026-08-25 10:24:21</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:36</t>
+          <t>2026-08-25 10:24:21</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-25_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:17</t>
+          <t>2026-08-25 17:35:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.45%2375</t>
+          <t>+1.05%2400</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2375</v>
+        <v>2400</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10.12%11,884,000</t>
+          <t>10.09%11,884,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10.12%</t>
+          <t>10.09%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:17</t>
+          <t>2026-08-25 17:35:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-4.4%5430</t>
+          <t>+3.04%5595</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>+3.04%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5430</v>
+        <v>5595</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.43%4,843,000</t>
+          <t>9.59%4,843,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.43%</t>
+          <t>9.59%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:17</t>
+          <t>2026-08-25 17:35:49</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.92%1075</t>
+          <t>+1.86%1095</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1075</v>
+        <v>1095</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7.83%20,300,000</t>
+          <t>7.86%20,300,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.83%</t>
+          <t>7.86%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:17</t>
+          <t>2026-08-25 17:35:49</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.66%3765</t>
+          <t>-0.8%3735</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3765</v>
+        <v>3735</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.95%5,148,000</t>
+          <t>6.80%5,148,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.95%</t>
+          <t>6.80%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:17</t>
+          <t>2026-08-25 17:35:49</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.35%2855</t>
+          <t>+3.33%2950</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>+3.33%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2855</v>
+        <v>2950</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.04%5,899,000</t>
+          <t>6.16%5,899,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.04%</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:17</t>
+          <t>2026-08-25 17:35:49</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+0.72%6300</t>
+          <t>+2.22%6440</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+0.72%</t>
+          <t>+2.22%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>6300</v>
+        <v>6440</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.03%2,226,000</t>
+          <t>5.07%2,226,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.03%</t>
+          <t>5.07%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:17</t>
+          <t>2026-08-25 17:35:49</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.54%551</t>
+          <t>+0.63%5600</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>551</v>
+        <v>5600</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.02%25,387,000</t>
+          <t>4.93%2,486,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.02%</t>
+          <t>4.93%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>25387000</v>
+        <v>2486000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:17</t>
+          <t>2026-08-25 17:35:49</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+1.83%5565</t>
+          <t>-1.27%544</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+1.83%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5565</v>
+        <v>544</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.96%2,486,000</t>
+          <t>4.89%25,387,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.96%</t>
+          <t>4.89%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2486000</v>
+        <v>25387000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:17</t>
+          <t>2026-08-25 17:35:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+1.72%2070</t>
+          <t>-1.93%2030</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+1.72%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2070</v>
+        <v>2030</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.87%6,564,000</t>
+          <t>4.71%6,564,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.87%</t>
+          <t>4.71%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:17</t>
+          <t>2026-08-25 17:35:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-4.45%5155</t>
+          <t>+0.97%5205</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-4.45%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5155</v>
+        <v>5205</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.45%2,407,000</t>
+          <t>4.43%2,407,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.45%</t>
+          <t>4.43%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:17</t>
+          <t>2026-08-25 17:35:49</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.86%1735</t>
+          <t>-1.44%1710</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1735</v>
+        <v>1710</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.38%7,040,000</t>
+          <t>4.26%7,040,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.38%</t>
+          <t>4.26%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:17</t>
+          <t>2026-08-25 17:35:49</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+0.85%592</t>
+          <t>-0.17%591</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.14%19,479,000</t>
+          <t>4.07%19,479,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4.14%</t>
+          <t>4.07%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:17</t>
+          <t>2026-08-25 17:35:49</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+6.01%123.5</t>
+          <t>+1.21%125</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+6.01%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>123.5</v>
+        <v>125</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.97%89,518,000</t>
+          <t>3.96%89,518,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.97%</t>
+          <t>3.96%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:17</t>
+          <t>2026-08-25 17:35:49</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0%1135</t>
+          <t>+2.2%1160</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+2.2%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1135</v>
+        <v>1160</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.92%9,624,000</t>
+          <t>3.95%9,624,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.92%</t>
+          <t>3.95%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:17</t>
+          <t>2026-08-25 17:35:49</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-9.89%2050</t>
+          <t>+1.22%2075</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-9.89%</t>
+          <t>+1.22%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2050</v>
+        <v>2075</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.44%4,671,848</t>
+          <t>3.43%4,671,848</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.44%</t>
+          <t>3.43%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:18</t>
+          <t>2026-08-25 17:36:01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,27 +1424,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.68%1455</t>
+          <t>+2.06%1485</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-2.68%</t>
+          <t>+2.06%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.87%5,498,000</t>
+          <t>2.89%5,498,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>2.89%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:18</t>
+          <t>2026-08-25 17:36:01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1487,27 +1487,27 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-1.53%15115</t>
+          <t>+1.89%15400</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-1.53%</t>
+          <t>+1.89%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>15115</t>
+          <t>15400</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.08%383,900</t>
+          <t>2.09%383,900</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.09%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:18</t>
+          <t>2026-08-25 17:36:01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1550,27 +1550,27 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-3.12%1710</t>
+          <t>+7.89%1845</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-3.12%</t>
+          <t>+7.89%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.39%2,264,000</t>
+          <t>1.48%2,264,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:18</t>
+          <t>2026-08-25 17:36:01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1613,27 +1613,27 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+3.02%239</t>
+          <t>+0.21%239.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+3.02%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>239.5</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.97%11,275,450</t>
+          <t>0.96%11,275,450</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:18</t>
+          <t>2026-08-25 17:36:01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1676,27 +1676,27 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+2.44%967</t>
+          <t>-0.21%965</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+2.44%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>965</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.86%2,477,000</t>
+          <t>0.85%2,477,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:18</t>
+          <t>2026-08-25 17:36:01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1739,17 +1739,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-1.76%948</t>
+          <t>+2.43%971</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-1.76%</t>
+          <t>+2.43%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>971</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:18</t>
+          <t>2026-08-25 17:36:01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1802,27 +1802,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+5.05%1145</t>
+          <t>+6.11%1215</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+5.05%</t>
+          <t>+6.11%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.53%1,301,000</t>
+          <t>0.56%1,301,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:18</t>
+          <t>2026-08-25 17:36:01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1860,40 +1860,40 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>4979華星光</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-4.2%5365</t>
+          <t>+9.87%601</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>+9.87%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>5365</t>
+          <t>601</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.49%255,000</t>
+          <t>0.52%2,424,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>255000</v>
+        <v>2424000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:18</t>
+          <t>2026-08-25 17:36:01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1923,40 +1923,40 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>4979華星光</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-5.2%547</t>
+          <t>+3.82%5570</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>+3.82%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>5570</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.48%2,424,000</t>
+          <t>0.50%255,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>2424000</v>
+        <v>255000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:18</t>
+          <t>2026-08-25 17:36:01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1986,27 +1986,27 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6510精測</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0%2650</t>
+          <t>+3.65%213</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+3.65%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>213</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.45%477,000</t>
+          <t>0.45%5,917,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2015,11 +2015,11 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>477000</v>
+        <v>5917000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:18</t>
+          <t>2026-08-25 17:36:01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2049,36 +2049,36 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>6510精測</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+1.23%205.5</t>
+          <t>+1.13%2680</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>205.5</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.44%5,917,000</t>
+          <t>0.45%477,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>5917000</v>
+        <v>477000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:18</t>
+          <t>2026-08-25 17:36:01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2117,17 +2117,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-1.25%435.5</t>
+          <t>+1.95%444</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-1.25%</t>
+          <t>+1.95%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>435.5</t>
+          <t>444</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:18</t>
+          <t>2026-08-25 17:36:01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2175,40 +2175,40 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6278台表科</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-4.28%179</t>
+          <t>+5.39%1270</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-4.28%</t>
+          <t>+5.39%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.21%3,249,000</t>
+          <t>0.22%483,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>3249000</v>
+        <v>483000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:18</t>
+          <t>2026-08-25 17:36:01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2238,27 +2238,27 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>6278台表科</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+0.84%1205</t>
+          <t>+1.4%181.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+0.84%</t>
+          <t>+1.4%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>181.5</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.21%483,000</t>
+          <t>0.21%3,249,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>483000</v>
+        <v>3249000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:19</t>
+          <t>2026-08-25 17:36:02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2306,25 +2306,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+0.26%193</t>
+          <t>+3.37%199.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+3.37%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>193</v>
+        <v>199.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.15%2,223,000</t>
+          <t>0.16%2,223,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:19</t>
+          <t>2026-08-25 17:36:02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2362,25 +2362,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6191精成科</t>
+          <t>3376新日興</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-1.1%81.1</t>
+          <t>+1.34%189</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>+1.34%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>81.09999999999999</v>
+        <v>189</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.12%3,988,000</t>
+          <t>0.12%1,741,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2389,11 +2389,11 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>3988000</v>
+        <v>1741000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:19</t>
+          <t>2026-08-25 17:36:02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2423,38 +2423,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3376新日興</t>
+          <t>6191精成科</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+1.91%186.5</t>
+          <t>-0.25%80.9</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+1.91%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>186.5</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.12%1,741,000</t>
+          <t>0.11%3,988,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.11%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>1741000</v>
+        <v>3988000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:19</t>
+          <t>2026-08-25 17:36:02</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2484,34 +2484,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2002中鋼</t>
+          <t>4966譜瑞-KY</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-1.29%19.2</t>
+          <t>-0.18%556</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>19.2</v>
+        <v>556</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.04%5,163,000</t>
+          <t>0.03%140,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.03%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>5163000</v>
+        <v>140000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:19</t>
+          <t>2026-08-25 17:36:02</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2545,25 +2545,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4966譜瑞-KY</t>
+          <t>2002中鋼</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.59%557</t>
+          <t>-0.78%19.05</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.59%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>557</v>
+        <v>19.05</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.03%140,000</t>
+          <t>0.03%5,163,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>140000</v>
+        <v>5163000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:19</t>
+          <t>2026-08-25 17:36:02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2611,16 +2611,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-4.36%417</t>
+          <t>+2.88%429</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-4.36%</t>
+          <t>+2.88%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:19</t>
+          <t>2026-08-25 17:36:02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2672,16 +2672,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+0.95%3735</t>
+          <t>+3.48%3865</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+0.95%</t>
+          <t>+3.48%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>3735</v>
+        <v>3865</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:19</t>
+          <t>2026-08-25 17:36:02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-0.12%82.4</t>
+          <t>-0.12%82.3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2742,7 +2742,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:19</t>
+          <t>2026-08-25 17:36:02</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2794,16 +2794,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0%1435</t>
+          <t>+1.74%1460</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.74%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1435</v>
+        <v>1460</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:19</t>
+          <t>2026-08-25 17:36:02</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2855,16 +2855,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-4.01%5385</t>
+          <t>+6.22%5720</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-4.01%</t>
+          <t>+6.22%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>5385</v>
+        <v>5720</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:19</t>
+          <t>2026-08-25 17:36:02</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2916,16 +2916,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+1.09%325</t>
+          <t>+1.08%328.5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>325</v>
+        <v>328.5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:19</t>
+          <t>2026-08-25 17:36:02</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2977,16 +2977,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-5.11%501</t>
+          <t>+1.8%510</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-5.11%</t>
+          <t>+1.8%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:19</t>
+          <t>2026-08-25 17:36:02</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3038,16 +3038,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-4.8%97.1</t>
+          <t>-1.65%95.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-1.65%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>97.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:19</t>
+          <t>2026-08-25 17:36:02</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3099,16 +3099,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-3.98%6145</t>
+          <t>+1.79%6255</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-3.98%</t>
+          <t>+1.79%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>6145</v>
+        <v>6255</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:19</t>
+          <t>2026-08-25 17:36:02</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3160,16 +3160,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-1.43%2070</t>
+          <t>-5.07%1965</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-5.07%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2070</v>
+        <v>1965</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:21</t>
+          <t>2026-08-25 17:36:03</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3221,16 +3221,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+7.33%1010</t>
+          <t>-2.97%980</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+7.33%</t>
+          <t>-2.97%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1010</v>
+        <v>980</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:21</t>
+          <t>2026-08-25 17:36:03</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3282,16 +3282,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-0.47%212.5</t>
+          <t>+2.35%217.5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>+2.35%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>212.5</v>
+        <v>217.5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:21</t>
+          <t>2026-08-25 17:36:03</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3343,16 +3343,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+1.15%87.7</t>
+          <t>-0.23%87.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+1.15%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>87.7</v>
+        <v>87.5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:21</t>
+          <t>2026-08-25 17:36:03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3404,16 +3404,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-0.81%243.5</t>
+          <t>-0.21%243</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-0.81%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>243.5</v>
+        <v>243</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:21</t>
+          <t>2026-08-25 17:36:03</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-0.33%151</t>
+          <t>-0.33%150.5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3474,7 +3474,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>151</v>
+        <v>150.5</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:21</t>
+          <t>2026-08-25 17:36:03</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3526,16 +3526,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+0.75%134</t>
+          <t>+2.24%137</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+0.75%</t>
+          <t>+2.24%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-08-25_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 17:35:49</t>
+          <t>2026-08-25 19:50:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 17:35:49</t>
+          <t>2026-08-25 19:50:48</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 17:35:49</t>
+          <t>2026-08-25 19:50:48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 17:35:49</t>
+          <t>2026-08-25 19:50:48</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 17:35:49</t>
+          <t>2026-08-25 19:50:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 17:35:49</t>
+          <t>2026-08-25 19:50:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 17:35:49</t>
+          <t>2026-08-25 19:50:48</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 17:35:49</t>
+          <t>2026-08-25 19:50:48</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 17:35:49</t>
+          <t>2026-08-25 19:50:48</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 17:35:49</t>
+          <t>2026-08-25 19:50:48</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 17:35:49</t>
+          <t>2026-08-25 19:50:48</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 17:35:49</t>
+          <t>2026-08-25 19:50:48</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 17:35:49</t>
+          <t>2026-08-25 19:50:48</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 17:35:49</t>
+          <t>2026-08-25 19:50:48</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 17:35:49</t>
+          <t>2026-08-25 19:50:48</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:01</t>
+          <t>2026-08-25 19:50:51</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:01</t>
+          <t>2026-08-25 19:50:51</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:01</t>
+          <t>2026-08-25 19:50:51</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:01</t>
+          <t>2026-08-25 19:50:51</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:01</t>
+          <t>2026-08-25 19:50:51</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:01</t>
+          <t>2026-08-25 19:50:51</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:01</t>
+          <t>2026-08-25 19:50:51</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:01</t>
+          <t>2026-08-25 19:50:51</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:01</t>
+          <t>2026-08-25 19:50:51</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:01</t>
+          <t>2026-08-25 19:50:51</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:01</t>
+          <t>2026-08-25 19:50:51</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:01</t>
+          <t>2026-08-25 19:50:51</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:01</t>
+          <t>2026-08-25 19:50:51</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:01</t>
+          <t>2026-08-25 19:50:51</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:02</t>
+          <t>2026-08-25 19:50:52</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:02</t>
+          <t>2026-08-25 19:50:52</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:02</t>
+          <t>2026-08-25 19:50:52</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:02</t>
+          <t>2026-08-25 19:50:52</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:02</t>
+          <t>2026-08-25 19:50:52</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:02</t>
+          <t>2026-08-25 19:50:52</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:02</t>
+          <t>2026-08-25 19:50:52</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:02</t>
+          <t>2026-08-25 19:50:52</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:02</t>
+          <t>2026-08-25 19:50:52</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:02</t>
+          <t>2026-08-25 19:50:52</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:02</t>
+          <t>2026-08-25 19:50:52</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:02</t>
+          <t>2026-08-25 19:50:52</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:02</t>
+          <t>2026-08-25 19:50:52</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:02</t>
+          <t>2026-08-25 19:50:52</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:02</t>
+          <t>2026-08-25 19:50:52</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:03</t>
+          <t>2026-08-25 19:50:54</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:03</t>
+          <t>2026-08-25 19:50:54</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:03</t>
+          <t>2026-08-25 19:50:54</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:03</t>
+          <t>2026-08-25 19:50:54</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:03</t>
+          <t>2026-08-25 19:50:54</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 17:36:03</t>
+          <t>2026-08-25 19:50:54</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-25_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:48</t>
+          <t>2026-08-25 21:08:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:51</t>
+          <t>2026-08-25 21:08:51</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:51</t>
+          <t>2026-08-25 21:08:51</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:51</t>
+          <t>2026-08-25 21:08:51</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:51</t>
+          <t>2026-08-25 21:08:51</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:51</t>
+          <t>2026-08-25 21:08:51</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:51</t>
+          <t>2026-08-25 21:08:51</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:51</t>
+          <t>2026-08-25 21:08:51</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:51</t>
+          <t>2026-08-25 21:08:51</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:51</t>
+          <t>2026-08-25 21:08:51</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:51</t>
+          <t>2026-08-25 21:08:51</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:51</t>
+          <t>2026-08-25 21:08:51</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:51</t>
+          <t>2026-08-25 21:08:51</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:51</t>
+          <t>2026-08-25 21:08:51</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:51</t>
+          <t>2026-08-25 21:08:51</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:52</t>
+          <t>2026-08-25 21:09:03</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:54</t>
+          <t>2026-08-25 21:09:14</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:54</t>
+          <t>2026-08-25 21:09:14</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:54</t>
+          <t>2026-08-25 21:09:14</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:54</t>
+          <t>2026-08-25 21:09:14</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:54</t>
+          <t>2026-08-25 21:09:14</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 19:50:54</t>
+          <t>2026-08-25 21:09:14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-25_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:40</t>
+          <t>2026-08-25 21:27:46</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:51</t>
+          <t>2026-08-25 21:27:47</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:51</t>
+          <t>2026-08-25 21:27:47</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:51</t>
+          <t>2026-08-25 21:27:47</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:51</t>
+          <t>2026-08-25 21:27:47</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:51</t>
+          <t>2026-08-25 21:27:47</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:51</t>
+          <t>2026-08-25 21:27:47</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:51</t>
+          <t>2026-08-25 21:27:47</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:51</t>
+          <t>2026-08-25 21:27:47</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:51</t>
+          <t>2026-08-25 21:27:47</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:51</t>
+          <t>2026-08-25 21:27:47</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:51</t>
+          <t>2026-08-25 21:27:47</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:51</t>
+          <t>2026-08-25 21:27:47</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:51</t>
+          <t>2026-08-25 21:27:47</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 21:08:51</t>
+          <t>2026-08-25 21:27:47</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:03</t>
+          <t>2026-08-25 21:27:48</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:14</t>
+          <t>2026-08-25 21:27:50</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:14</t>
+          <t>2026-08-25 21:27:50</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:14</t>
+          <t>2026-08-25 21:27:50</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:14</t>
+          <t>2026-08-25 21:27:50</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:14</t>
+          <t>2026-08-25 21:27:50</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:14</t>
+          <t>2026-08-25 21:27:50</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-25_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:46</t>
+          <t>2026-08-25 21:31:04</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:47</t>
+          <t>2026-08-25 21:31:09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:47</t>
+          <t>2026-08-25 21:31:09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:47</t>
+          <t>2026-08-25 21:31:09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:47</t>
+          <t>2026-08-25 21:31:09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:47</t>
+          <t>2026-08-25 21:31:09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:47</t>
+          <t>2026-08-25 21:31:09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:47</t>
+          <t>2026-08-25 21:31:09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:47</t>
+          <t>2026-08-25 21:31:09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:47</t>
+          <t>2026-08-25 21:31:09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:47</t>
+          <t>2026-08-25 21:31:09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:47</t>
+          <t>2026-08-25 21:31:09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:47</t>
+          <t>2026-08-25 21:31:09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:47</t>
+          <t>2026-08-25 21:31:09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:47</t>
+          <t>2026-08-25 21:31:09</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:48</t>
+          <t>2026-08-25 21:31:10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:50</t>
+          <t>2026-08-25 21:31:12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:50</t>
+          <t>2026-08-25 21:31:12</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:50</t>
+          <t>2026-08-25 21:31:12</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:50</t>
+          <t>2026-08-25 21:31:12</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:50</t>
+          <t>2026-08-25 21:31:12</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 21:27:50</t>
+          <t>2026-08-25 21:31:12</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-25_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:04</t>
+          <t>2026-08-25 22:03:53</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:09</t>
+          <t>2026-08-25 22:03:55</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:09</t>
+          <t>2026-08-25 22:03:55</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:09</t>
+          <t>2026-08-25 22:03:55</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:09</t>
+          <t>2026-08-25 22:03:55</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:09</t>
+          <t>2026-08-25 22:03:55</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:09</t>
+          <t>2026-08-25 22:03:55</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:09</t>
+          <t>2026-08-25 22:03:55</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:09</t>
+          <t>2026-08-25 22:03:55</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:09</t>
+          <t>2026-08-25 22:03:55</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:09</t>
+          <t>2026-08-25 22:03:55</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:09</t>
+          <t>2026-08-25 22:03:55</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:09</t>
+          <t>2026-08-25 22:03:55</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:09</t>
+          <t>2026-08-25 22:03:55</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:09</t>
+          <t>2026-08-25 22:03:55</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:10</t>
+          <t>2026-08-25 22:03:56</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:12</t>
+          <t>2026-08-25 22:03:57</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:12</t>
+          <t>2026-08-25 22:03:57</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:12</t>
+          <t>2026-08-25 22:03:57</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:12</t>
+          <t>2026-08-25 22:03:57</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:12</t>
+          <t>2026-08-25 22:03:57</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:12</t>
+          <t>2026-08-25 22:03:57</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
